--- a/data/trans_orig/P16A_n_R2-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P16A_n_R2-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido dos o más medicamentos en las dos últimas semanas en 2007</t>
+          <t>Población que ha consumido dos o más medicamentos en las dos últimas semanas en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>99360</t>
+          <t>100651</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>137739</t>
+          <t>139378</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>158317</t>
+          <t>158983</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>204352</t>
+          <t>207439</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>30,14%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>269920</t>
+          <t>270915</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>330373</t>
+          <t>330040</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>23,88%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>556273</t>
+          <t>554634</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>594652</t>
+          <t>593361</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>80,15%</t>
+          <t>79,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,68%</t>
+          <t>85,5%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>483999</t>
+          <t>480912</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>530034</t>
+          <t>529368</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>70,31%</t>
+          <t>69,86%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>77,0%</t>
+          <t>76,9%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1051990</t>
+          <t>1052323</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1112443</t>
+          <t>1111448</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>76,1%</t>
+          <t>76,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>80,47%</t>
+          <t>80,4%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>150857</t>
+          <t>151664</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>200015</t>
+          <t>200614</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>252325</t>
+          <t>251073</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>308244</t>
+          <t>311497</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,83%</t>
+          <t>32,17%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>414917</t>
+          <t>416549</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>490756</t>
+          <t>493325</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>25,56%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>761785</t>
+          <t>761186</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>810943</t>
+          <t>810136</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>79,2%</t>
+          <t>79,14%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>84,32%</t>
+          <t>84,23%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>660149</t>
+          <t>656896</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>716068</t>
+          <t>717320</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>68,17%</t>
+          <t>67,83%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>73,94%</t>
+          <t>74,07%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1439437</t>
+          <t>1436868</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1515276</t>
+          <t>1513644</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>74,57%</t>
+          <t>74,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,5%</t>
+          <t>78,42%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>93243</t>
+          <t>92997</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>130959</t>
+          <t>131665</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>190180</t>
+          <t>189994</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>237346</t>
+          <t>238489</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>27,78%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,71%</t>
+          <t>34,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>291802</t>
+          <t>296029</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>354440</t>
+          <t>357405</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>26,23%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>547550</t>
+          <t>546844</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>585266</t>
+          <t>585512</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>80,7%</t>
+          <t>80,59%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>86,26%</t>
+          <t>86,29%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>446495</t>
+          <t>445352</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>493661</t>
+          <t>493847</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>65,29%</t>
+          <t>65,13%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>72,19%</t>
+          <t>72,22%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1007910</t>
+          <t>1004945</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1070548</t>
+          <t>1066321</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>73,98%</t>
+          <t>73,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>78,58%</t>
+          <t>78,27%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>145591</t>
+          <t>145594</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>190982</t>
+          <t>190829</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>305294</t>
+          <t>298968</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>364164</t>
+          <t>360596</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>28,79%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>35,06%</t>
+          <t>34,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>462434</t>
+          <t>464669</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>542940</t>
+          <t>544111</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>27,47%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>751240</t>
+          <t>751393</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>796631</t>
+          <t>796628</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,73%</t>
+          <t>79,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>674448</t>
+          <t>678016</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>733318</t>
+          <t>739644</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>64,94%</t>
+          <t>65,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>70,61%</t>
+          <t>71,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1437894</t>
+          <t>1436723</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1518400</t>
+          <t>1516165</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>72,59%</t>
+          <t>72,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>76,65%</t>
+          <t>76,54%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>528509</t>
+          <t>528764</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>612482</t>
+          <t>612259</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>951145</t>
+          <t>957519</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1064005</t>
+          <t>1062880</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>31,45%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1510894</t>
+          <t>1508901</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1648760</t>
+          <t>1646994</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>24,75%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2664061</t>
+          <t>2664284</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2748034</t>
+          <t>2747779</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2238,7 +2238,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>83,87%</t>
+          <t>83,86%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2315192</t>
+          <t>2316317</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2428052</t>
+          <t>2421678</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>68,51%</t>
+          <t>68,55%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>71,85%</t>
+          <t>71,66%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5006981</t>
+          <t>5008747</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5144847</t>
+          <t>5146840</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>75,23%</t>
+          <t>75,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>77,3%</t>
+          <t>77,33%</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido dos o más medicamentos en las dos últimas semanas en 2012</t>
+          <t>Población que ha consumido dos o más medicamentos en las dos últimas semanas en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>170744</t>
+          <t>170800</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>220734</t>
+          <t>216397</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>30,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>263997</t>
+          <t>269600</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>319647</t>
+          <t>319546</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>37,87%</t>
+          <t>38,68%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>45,86%</t>
+          <t>45,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>451868</t>
+          <t>450220</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>529112</t>
+          <t>524764</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>32,26%</t>
+          <t>32,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>37,78%</t>
+          <t>37,47%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>482735</t>
+          <t>487072</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>532725</t>
+          <t>532669</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>68,62%</t>
+          <t>69,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>75,73%</t>
+          <t>75,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>377403</t>
+          <t>377504</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>433053</t>
+          <t>427450</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>54,14%</t>
+          <t>54,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>62,13%</t>
+          <t>61,32%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>871407</t>
+          <t>875755</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>948651</t>
+          <t>950299</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>62,22%</t>
+          <t>62,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>67,74%</t>
+          <t>67,85%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>222744</t>
+          <t>222222</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>283703</t>
+          <t>278234</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>27,33%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>357388</t>
+          <t>348975</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>419581</t>
+          <t>416794</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>33,81%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>40,65%</t>
+          <t>40,38%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>597362</t>
+          <t>595873</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>682436</t>
+          <t>682564</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,7 +3108,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>29,07%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>734244</t>
+          <t>739713</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>795203</t>
+          <t>795725</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>72,13%</t>
+          <t>72,67%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>78,12%</t>
+          <t>78,17%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>612603</t>
+          <t>615390</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>674796</t>
+          <t>683209</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>59,35%</t>
+          <t>59,62%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>65,38%</t>
+          <t>66,19%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1367695</t>
+          <t>1367567</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1452769</t>
+          <t>1454258</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>70,86%</t>
+          <t>70,93%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>143306</t>
+          <t>145063</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>193395</t>
+          <t>193875</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,59%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>274419</t>
+          <t>276183</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>332069</t>
+          <t>333517</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>35,31%</t>
+          <t>35,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>42,73%</t>
+          <t>42,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>436636</t>
+          <t>438451</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>511089</t>
+          <t>511146</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>28,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>564228</t>
+          <t>563748</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>614317</t>
+          <t>612560</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>74,47%</t>
+          <t>74,41%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>81,08%</t>
+          <t>80,85%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>445105</t>
+          <t>443657</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>502755</t>
+          <t>500991</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>57,27%</t>
+          <t>57,09%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>64,69%</t>
+          <t>64,46%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1023708</t>
+          <t>1023651</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1098161</t>
+          <t>1096346</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3569,7 +3569,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>71,55%</t>
+          <t>71,43%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>224157</t>
+          <t>221700</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>280676</t>
+          <t>280517</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>23,39%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>29,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>405249</t>
+          <t>406729</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>471501</t>
+          <t>471945</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>38,53%</t>
+          <t>38,67%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>44,82%</t>
+          <t>44,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>646286</t>
+          <t>650557</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>736653</t>
+          <t>742505</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>32,32%</t>
+          <t>32,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>36,84%</t>
+          <t>37,13%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>667063</t>
+          <t>667222</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>723582</t>
+          <t>726039</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>70,38%</t>
+          <t>70,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>76,35%</t>
+          <t>76,61%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>580400</t>
+          <t>579956</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>646652</t>
+          <t>645172</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>55,18%</t>
+          <t>55,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>61,47%</t>
+          <t>61,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1262987</t>
+          <t>1257135</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1353354</t>
+          <t>1349083</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>63,16%</t>
+          <t>62,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>67,68%</t>
+          <t>67,47%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>815615</t>
+          <t>813379</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>920105</t>
+          <t>919139</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>26,82%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1365655</t>
+          <t>1364502</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1482575</t>
+          <t>1482274</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>38,38%</t>
+          <t>38,35%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>41,67%</t>
+          <t>41,66%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2210371</t>
+          <t>2212676</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2375709</t>
+          <t>2370765</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>31,68%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>34,01%</t>
+          <t>33,94%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2506674</t>
+          <t>2507640</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2611164</t>
+          <t>2613400</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>73,15%</t>
+          <t>73,18%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>76,2%</t>
+          <t>76,26%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2075734</t>
+          <t>2076035</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2192654</t>
+          <t>2193807</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>58,33%</t>
+          <t>58,34%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>61,62%</t>
+          <t>61,65%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4609379</t>
+          <t>4614323</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4774717</t>
+          <t>4772412</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>65,99%</t>
+          <t>66,06%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>68,36%</t>
+          <t>68,32%</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido dos o más medicamentos en las dos últimas semanas en 2016</t>
+          <t>Población que ha consumido dos o más medicamentos en las dos últimas semanas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>130477</t>
+          <t>131138</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>172032</t>
+          <t>173662</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>221785</t>
+          <t>223796</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>274957</t>
+          <t>275521</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>32,96%</t>
+          <t>33,26%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>40,87%</t>
+          <t>40,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>366157</t>
+          <t>368677</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>432061</t>
+          <t>433465</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>27,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>32,16%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>502768</t>
+          <t>501138</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>544323</t>
+          <t>543662</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>74,51%</t>
+          <t>74,26%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,66%</t>
+          <t>80,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>397882</t>
+          <t>397318</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>451054</t>
+          <t>449043</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>59,13%</t>
+          <t>59,05%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>67,04%</t>
+          <t>66,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>915578</t>
+          <t>914174</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>981482</t>
+          <t>978962</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>67,94%</t>
+          <t>67,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>72,83%</t>
+          <t>72,64%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>211440</t>
+          <t>210945</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>265178</t>
+          <t>263504</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>322572</t>
+          <t>321962</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>386639</t>
+          <t>386653</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,7 +5020,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>30,87%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>546383</t>
+          <t>550708</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>631692</t>
+          <t>634597</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>30,73%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>757253</t>
+          <t>758927</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>810991</t>
+          <t>811486</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>74,06%</t>
+          <t>74,23%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>79,32%</t>
+          <t>79,37%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>656274</t>
+          <t>656260</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>720341</t>
+          <t>720951</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>69,07%</t>
+          <t>69,13%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1433652</t>
+          <t>1430747</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1518961</t>
+          <t>1514636</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>69,41%</t>
+          <t>69,27%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>73,55%</t>
+          <t>73,34%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>137805</t>
+          <t>137249</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>183666</t>
+          <t>185301</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>212497</t>
+          <t>211915</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>269063</t>
+          <t>267347</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>27,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,28%</t>
+          <t>34,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>365545</t>
+          <t>364258</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>439158</t>
+          <t>434856</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>28,15%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>575886</t>
+          <t>574251</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>621747</t>
+          <t>622303</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>75,82%</t>
+          <t>75,6%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>81,86%</t>
+          <t>81,93%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>515948</t>
+          <t>517664</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>572514</t>
+          <t>573096</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>65,72%</t>
+          <t>65,94%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>72,93%</t>
+          <t>73,0%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1105405</t>
+          <t>1109707</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1179018</t>
+          <t>1180305</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>71,57%</t>
+          <t>71,85%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>76,33%</t>
+          <t>76,42%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>205142</t>
+          <t>206428</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>255703</t>
+          <t>257473</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>27,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>362791</t>
+          <t>361216</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>426227</t>
+          <t>425669</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>34,76%</t>
+          <t>34,61%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>40,83%</t>
+          <t>40,78%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>580989</t>
+          <t>581851</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>669621</t>
+          <t>666082</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>29,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>33,62%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>681864</t>
+          <t>680094</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>732425</t>
+          <t>731139</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>72,73%</t>
+          <t>72,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>78,12%</t>
+          <t>77,98%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>617552</t>
+          <t>618110</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>680988</t>
+          <t>682563</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>59,17%</t>
+          <t>59,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>65,24%</t>
+          <t>65,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1311725</t>
+          <t>1315264</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1400357</t>
+          <t>1399495</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>66,2%</t>
+          <t>66,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>70,68%</t>
+          <t>70,63%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>730904</t>
+          <t>728195</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>829383</t>
+          <t>826325</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1172285</t>
+          <t>1179342</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1289757</t>
+          <t>1295341</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>33,07%</t>
+          <t>33,27%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>36,39%</t>
+          <t>36,54%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1937437</t>
+          <t>1929719</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2091778</t>
+          <t>2086393</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>27,81%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,15%</t>
+          <t>30,07%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2564967</t>
+          <t>2568025</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2663446</t>
+          <t>2666155</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>75,57%</t>
+          <t>75,66%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>78,47%</t>
+          <t>78,55%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2254785</t>
+          <t>2249201</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2372257</t>
+          <t>2365200</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>63,61%</t>
+          <t>63,46%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>66,93%</t>
+          <t>66,73%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4847114</t>
+          <t>4852499</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5001455</t>
+          <t>5009173</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>69,85%</t>
+          <t>69,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>72,08%</t>
+          <t>72,19%</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido dos o más medicamentos en las dos últimas semanas en 2023</t>
+          <t>Población que ha consumido dos o más medicamentos en las dos últimas semanas en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>183236</t>
+          <t>183390</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>228353</t>
+          <t>229141</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>28,86%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>35,94%</t>
+          <t>36,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>233178</t>
+          <t>227413</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>322430</t>
+          <t>319859</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>31,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>44,45%</t>
+          <t>44,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>431118</t>
+          <t>446763</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>532311</t>
+          <t>534998</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>31,68%</t>
+          <t>32,83%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>39,12%</t>
+          <t>39,32%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>407088</t>
+          <t>406300</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>452205</t>
+          <t>452051</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>64,06%</t>
+          <t>63,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>71,16%</t>
+          <t>71,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>402900</t>
+          <t>405471</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>492152</t>
+          <t>497917</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>55,55%</t>
+          <t>55,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>67,85%</t>
+          <t>68,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>828461</t>
+          <t>825774</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>929654</t>
+          <t>914009</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>60,88%</t>
+          <t>60,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>68,32%</t>
+          <t>67,17%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>137471</t>
+          <t>116265</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>324948</t>
+          <t>320883</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>362320</t>
+          <t>360619</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>415260</t>
+          <t>412054</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>37,79%</t>
+          <t>37,62%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>43,32%</t>
+          <t>42,98%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>428793</t>
+          <t>432068</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>727598</t>
+          <t>724598</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>33,68%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>867916</t>
+          <t>871981</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1055393</t>
+          <t>1076599</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>72,76%</t>
+          <t>73,1%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,48%</t>
+          <t>90,25%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>543391</t>
+          <t>546597</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>596331</t>
+          <t>598032</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>56,68%</t>
+          <t>57,02%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>62,21%</t>
+          <t>62,38%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1423918</t>
+          <t>1426918</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1722723</t>
+          <t>1719448</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>66,18%</t>
+          <t>66,32%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>80,07%</t>
+          <t>79,92%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>187919</t>
+          <t>186567</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>241275</t>
+          <t>236654</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>26,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>33,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>330669</t>
+          <t>329112</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>680252</t>
+          <t>705811</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>35,43%</t>
+          <t>35,26%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>72,88%</t>
+          <t>75,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>535607</t>
+          <t>532692</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1015749</t>
+          <t>988850</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>32,7%</t>
+          <t>32,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>62,01%</t>
+          <t>60,37%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>463405</t>
+          <t>468026</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>516761</t>
+          <t>518113</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>65,76%</t>
+          <t>66,42%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>73,33%</t>
+          <t>73,52%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>253114</t>
+          <t>227555</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>602697</t>
+          <t>604254</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>64,57%</t>
+          <t>64,74%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>622297</t>
+          <t>649196</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1102439</t>
+          <t>1105354</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>37,99%</t>
+          <t>39,63%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>67,3%</t>
+          <t>67,48%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>267430</t>
+          <t>268077</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>326391</t>
+          <t>325198</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>28,92%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,22%</t>
+          <t>35,09%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>350198</t>
+          <t>355721</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>476431</t>
+          <t>482392</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>32,49%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>43,51%</t>
+          <t>44,06%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>638683</t>
+          <t>651981</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>783227</t>
+          <t>780673</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>31,59%</t>
+          <t>32,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>38,74%</t>
+          <t>38,61%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>600440</t>
+          <t>601633</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>659401</t>
+          <t>658754</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>64,78%</t>
+          <t>64,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>71,15%</t>
+          <t>71,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>618501</t>
+          <t>612540</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>744734</t>
+          <t>739211</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>56,49%</t>
+          <t>55,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>68,02%</t>
+          <t>67,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1238536</t>
+          <t>1241090</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1383080</t>
+          <t>1369782</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>61,26%</t>
+          <t>61,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>68,41%</t>
+          <t>67,75%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>769346</t>
+          <t>738827</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1057510</t>
+          <t>1054383</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>30,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1435776</t>
+          <t>1433857</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2015906</t>
+          <t>1977414</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>38,68%</t>
+          <t>38,62%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>54,3%</t>
+          <t>53,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2299674</t>
+          <t>2316995</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3002654</t>
+          <t>2933743</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>32,31%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>41,87%</t>
+          <t>40,9%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2402307</t>
+          <t>2405434</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2690471</t>
+          <t>2720990</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>69,43%</t>
+          <t>69,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>77,76%</t>
+          <t>78,65%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1696374</t>
+          <t>1734866</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2276504</t>
+          <t>2278423</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>45,7%</t>
+          <t>46,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>61,32%</t>
+          <t>61,38%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4169443</t>
+          <t>4238354</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4872423</t>
+          <t>4855102</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>58,13%</t>
+          <t>59,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>67,94%</t>
+          <t>67,69%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P16A_n_R2-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P16A_n_R2-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>100651</t>
+          <t>100357</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>139378</t>
+          <t>138016</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>158983</t>
+          <t>159539</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>207439</t>
+          <t>203540</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>29,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>270915</t>
+          <t>270610</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>330040</t>
+          <t>329805</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>23,86%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>554634</t>
+          <t>555996</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>593361</t>
+          <t>593655</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>79,92%</t>
+          <t>80,11%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,5%</t>
+          <t>85,54%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>480912</t>
+          <t>484811</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>529368</t>
+          <t>528812</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>69,86%</t>
+          <t>70,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>76,9%</t>
+          <t>76,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1052323</t>
+          <t>1052558</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1111448</t>
+          <t>1111753</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>76,12%</t>
+          <t>76,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>80,4%</t>
+          <t>80,42%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>151664</t>
+          <t>151853</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>200614</t>
+          <t>197686</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>251073</t>
+          <t>249776</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>311497</t>
+          <t>308232</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>25,79%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>31,83%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>416549</t>
+          <t>416369</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>493325</t>
+          <t>491080</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>25,44%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>761186</t>
+          <t>764114</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>810136</t>
+          <t>809947</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>79,14%</t>
+          <t>79,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>84,23%</t>
+          <t>84,21%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>656896</t>
+          <t>660161</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>717320</t>
+          <t>718617</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>67,83%</t>
+          <t>68,17%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>74,07%</t>
+          <t>74,21%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1436868</t>
+          <t>1439113</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1513644</t>
+          <t>1513824</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>74,44%</t>
+          <t>74,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,42%</t>
+          <t>78,43%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>92997</t>
+          <t>92195</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>131665</t>
+          <t>130551</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>189994</t>
+          <t>187881</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>238489</t>
+          <t>235115</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,87%</t>
+          <t>34,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>296029</t>
+          <t>294222</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>357405</t>
+          <t>354243</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>26,0%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>546844</t>
+          <t>547958</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>585512</t>
+          <t>586314</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>80,59%</t>
+          <t>80,76%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>86,29%</t>
+          <t>86,41%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>445352</t>
+          <t>448726</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>493847</t>
+          <t>495960</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>65,13%</t>
+          <t>65,62%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>72,22%</t>
+          <t>72,53%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1004945</t>
+          <t>1008107</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1066321</t>
+          <t>1068128</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>73,77%</t>
+          <t>74,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>78,27%</t>
+          <t>78,4%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>145594</t>
+          <t>146758</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>190829</t>
+          <t>189371</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>298968</t>
+          <t>304002</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>360596</t>
+          <t>363341</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>29,27%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>34,72%</t>
+          <t>34,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>464669</t>
+          <t>462790</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>544111</t>
+          <t>539811</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>27,25%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>751393</t>
+          <t>752851</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>796628</t>
+          <t>795464</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,75%</t>
+          <t>79,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,55%</t>
+          <t>84,42%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>678016</t>
+          <t>675271</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>739644</t>
+          <t>734610</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>65,28%</t>
+          <t>65,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>71,21%</t>
+          <t>70,73%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1436723</t>
+          <t>1441023</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1516165</t>
+          <t>1518044</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>72,53%</t>
+          <t>72,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>76,54%</t>
+          <t>76,64%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>528764</t>
+          <t>531817</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>612259</t>
+          <t>613638</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>957519</t>
+          <t>956577</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1062880</t>
+          <t>1067183</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>28,31%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>31,58%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1508901</t>
+          <t>1507175</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1646994</t>
+          <t>1650446</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>22,64%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>24,8%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2664284</t>
+          <t>2662905</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2747779</t>
+          <t>2744726</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>81,31%</t>
+          <t>81,27%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>83,86%</t>
+          <t>83,77%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2316317</t>
+          <t>2312014</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2421678</t>
+          <t>2422620</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>68,55%</t>
+          <t>68,42%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>71,66%</t>
+          <t>71,69%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5008747</t>
+          <t>5005295</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5146840</t>
+          <t>5148566</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>75,25%</t>
+          <t>75,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>77,33%</t>
+          <t>77,36%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>170800</t>
+          <t>169057</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>216397</t>
+          <t>218399</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>30,76%</t>
+          <t>31,05%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>269600</t>
+          <t>265878</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>319546</t>
+          <t>318118</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>38,68%</t>
+          <t>38,14%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>45,84%</t>
+          <t>45,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>450220</t>
+          <t>448264</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>524764</t>
+          <t>522324</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>32,01%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>37,47%</t>
+          <t>37,3%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>487072</t>
+          <t>485070</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>532669</t>
+          <t>534412</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>69,24%</t>
+          <t>68,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>75,72%</t>
+          <t>75,97%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>377504</t>
+          <t>378932</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>427450</t>
+          <t>431172</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>54,16%</t>
+          <t>54,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>61,32%</t>
+          <t>61,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>875755</t>
+          <t>878195</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>950299</t>
+          <t>952255</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>62,53%</t>
+          <t>62,7%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>67,85%</t>
+          <t>67,99%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>222222</t>
+          <t>223909</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>278234</t>
+          <t>281816</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>27,68%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>348975</t>
+          <t>355286</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>416794</t>
+          <t>423060</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>33,81%</t>
+          <t>34,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>40,38%</t>
+          <t>40,99%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>595873</t>
+          <t>594117</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>682564</t>
+          <t>680341</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>28,98%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,29%</t>
+          <t>33,19%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>739713</t>
+          <t>736131</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>795725</t>
+          <t>794038</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>72,67%</t>
+          <t>72,32%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>78,17%</t>
+          <t>78,0%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>615390</t>
+          <t>609124</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>683209</t>
+          <t>676898</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>59,62%</t>
+          <t>59,01%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>66,19%</t>
+          <t>65,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1367567</t>
+          <t>1369790</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1454258</t>
+          <t>1456014</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>66,71%</t>
+          <t>66,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>70,93%</t>
+          <t>71,02%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>145063</t>
+          <t>147378</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>193875</t>
+          <t>196529</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>25,94%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>276183</t>
+          <t>274712</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>333517</t>
+          <t>331364</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>35,54%</t>
+          <t>35,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>42,91%</t>
+          <t>42,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>438451</t>
+          <t>433405</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>511146</t>
+          <t>511804</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>28,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>33,35%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>563748</t>
+          <t>561094</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>612560</t>
+          <t>610245</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>74,41%</t>
+          <t>74,06%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>80,85%</t>
+          <t>80,55%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>443657</t>
+          <t>445810</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>500991</t>
+          <t>502462</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>57,09%</t>
+          <t>57,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>64,46%</t>
+          <t>64,65%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1023651</t>
+          <t>1022993</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1096346</t>
+          <t>1101392</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>66,7%</t>
+          <t>66,65%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>71,43%</t>
+          <t>71,76%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>221700</t>
+          <t>226647</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>280517</t>
+          <t>286030</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>23,91%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>30,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>406729</t>
+          <t>408262</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>471945</t>
+          <t>470545</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>38,67%</t>
+          <t>38,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>44,87%</t>
+          <t>44,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>650557</t>
+          <t>649932</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>742505</t>
+          <t>737233</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>32,5%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>37,13%</t>
+          <t>36,87%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>667222</t>
+          <t>661709</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>726039</t>
+          <t>721092</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>70,4%</t>
+          <t>69,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>76,61%</t>
+          <t>76,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>579956</t>
+          <t>581356</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>645172</t>
+          <t>643639</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>55,13%</t>
+          <t>55,27%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>61,33%</t>
+          <t>61,19%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1257135</t>
+          <t>1262407</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1349083</t>
+          <t>1349708</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>62,87%</t>
+          <t>63,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>67,47%</t>
+          <t>67,5%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>813379</t>
+          <t>809215</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>919139</t>
+          <t>914675</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>26,69%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1364502</t>
+          <t>1369206</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1482274</t>
+          <t>1483275</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>38,35%</t>
+          <t>38,48%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>41,66%</t>
+          <t>41,68%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2212676</t>
+          <t>2210844</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2370765</t>
+          <t>2366137</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>31,68%</t>
+          <t>31,65%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>33,94%</t>
+          <t>33,87%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2507640</t>
+          <t>2512104</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2613400</t>
+          <t>2617564</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>73,18%</t>
+          <t>73,31%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>76,26%</t>
+          <t>76,39%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2076035</t>
+          <t>2075034</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2193807</t>
+          <t>2189103</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>58,34%</t>
+          <t>58,32%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>61,65%</t>
+          <t>61,52%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4614323</t>
+          <t>4618951</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4772412</t>
+          <t>4774244</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>66,06%</t>
+          <t>66,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>68,32%</t>
+          <t>68,35%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>131138</t>
+          <t>129873</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>173662</t>
+          <t>175323</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>25,98%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>223796</t>
+          <t>222175</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>275521</t>
+          <t>271002</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>33,26%</t>
+          <t>33,02%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>40,95%</t>
+          <t>40,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>368677</t>
+          <t>365869</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>433465</t>
+          <t>434323</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>27,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>32,16%</t>
+          <t>32,23%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>501138</t>
+          <t>499477</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>543662</t>
+          <t>544927</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>74,26%</t>
+          <t>74,02%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,57%</t>
+          <t>80,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>397318</t>
+          <t>401837</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>449043</t>
+          <t>450664</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>59,05%</t>
+          <t>59,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>66,74%</t>
+          <t>66,98%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>914174</t>
+          <t>913316</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>978962</t>
+          <t>981770</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>67,84%</t>
+          <t>67,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>72,64%</t>
+          <t>72,85%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>210945</t>
+          <t>211385</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>263504</t>
+          <t>269342</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>26,34%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>321962</t>
+          <t>324222</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>386653</t>
+          <t>388758</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>31,09%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>37,07%</t>
+          <t>37,28%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>550708</t>
+          <t>548848</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>634597</t>
+          <t>632683</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>26,57%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>30,63%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>758927</t>
+          <t>753089</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>811486</t>
+          <t>811046</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>74,23%</t>
+          <t>73,66%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>79,37%</t>
+          <t>79,33%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>656260</t>
+          <t>654155</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>720951</t>
+          <t>718691</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>62,93%</t>
+          <t>62,72%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>69,13%</t>
+          <t>68,91%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1430747</t>
+          <t>1432661</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1514636</t>
+          <t>1516496</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>69,27%</t>
+          <t>69,37%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>73,34%</t>
+          <t>73,43%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>137249</t>
+          <t>138312</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>185301</t>
+          <t>184272</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>211915</t>
+          <t>213540</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>267347</t>
+          <t>267564</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>27,0%</t>
+          <t>27,2%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,06%</t>
+          <t>34,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>364258</t>
+          <t>361629</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>434856</t>
+          <t>433237</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>28,05%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>574251</t>
+          <t>575280</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>622303</t>
+          <t>621240</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>75,6%</t>
+          <t>75,74%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>81,93%</t>
+          <t>81,79%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>517664</t>
+          <t>517447</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>573096</t>
+          <t>571471</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>65,94%</t>
+          <t>65,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>73,0%</t>
+          <t>72,8%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1109707</t>
+          <t>1111326</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1180305</t>
+          <t>1182934</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>71,85%</t>
+          <t>71,95%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>76,42%</t>
+          <t>76,59%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>206428</t>
+          <t>204668</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>257473</t>
+          <t>256646</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>27,37%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>361216</t>
+          <t>362670</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>425669</t>
+          <t>431438</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>34,61%</t>
+          <t>34,75%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>40,78%</t>
+          <t>41,33%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>581851</t>
+          <t>582784</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>666082</t>
+          <t>669317</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>29,41%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,62%</t>
+          <t>33,78%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>680094</t>
+          <t>680921</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>731139</t>
+          <t>732899</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>72,54%</t>
+          <t>72,63%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>77,98%</t>
+          <t>78,17%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>618110</t>
+          <t>612341</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>682563</t>
+          <t>681109</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>59,22%</t>
+          <t>58,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>65,39%</t>
+          <t>65,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1315264</t>
+          <t>1312029</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1399495</t>
+          <t>1398562</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>66,38%</t>
+          <t>66,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>70,63%</t>
+          <t>70,59%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>728195</t>
+          <t>731051</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>826325</t>
+          <t>828740</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1179342</t>
+          <t>1177292</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1295341</t>
+          <t>1295952</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>33,21%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>36,54%</t>
+          <t>36,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1929719</t>
+          <t>1938917</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2086393</t>
+          <t>2087176</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>27,94%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>30,08%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2568025</t>
+          <t>2565610</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2666155</t>
+          <t>2663299</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>75,66%</t>
+          <t>75,58%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>78,55%</t>
+          <t>78,46%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2249201</t>
+          <t>2248590</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2365200</t>
+          <t>2367250</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>63,46%</t>
+          <t>63,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>66,73%</t>
+          <t>66,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4852499</t>
+          <t>4851716</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5009173</t>
+          <t>4999975</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>69,93%</t>
+          <t>69,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>72,19%</t>
+          <t>72,06%</t>
         </is>
       </c>
     </row>
@@ -6569,32 +6569,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>204999</t>
+          <t>221870</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>183390</t>
+          <t>195936</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>229141</t>
+          <t>249126</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>32,26%</t>
+          <t>32,12%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>36,06%</t>
+          <t>36,07%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6604,32 +6604,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>290915</t>
+          <t>310487</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>227413</t>
+          <t>288827</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>319859</t>
+          <t>332757</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>40,11%</t>
+          <t>42,29%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>39,34%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>44,1%</t>
+          <t>45,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>495914</t>
+          <t>532357</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>446763</t>
+          <t>500357</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>534998</t>
+          <t>566159</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>36,44%</t>
+          <t>37,36%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>32,83%</t>
+          <t>35,12%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>39,32%</t>
+          <t>39,73%</t>
         </is>
       </c>
     </row>
@@ -6682,32 +6682,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>430442</t>
+          <t>468840</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>406300</t>
+          <t>441584</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>452051</t>
+          <t>494774</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>67,74%</t>
+          <t>67,88%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>63,94%</t>
+          <t>63,93%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>71,14%</t>
+          <t>71,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6717,32 +6717,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>434415</t>
+          <t>423693</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>405471</t>
+          <t>401423</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>497917</t>
+          <t>445353</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>59,89%</t>
+          <t>57,71%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>55,9%</t>
+          <t>54,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>68,65%</t>
+          <t>60,66%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>864858</t>
+          <t>892532</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>825774</t>
+          <t>858730</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>914009</t>
+          <t>924532</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>63,56%</t>
+          <t>62,64%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>60,68%</t>
+          <t>60,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>67,17%</t>
+          <t>64,88%</t>
         </is>
       </c>
     </row>
@@ -6795,17 +6795,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6830,17 +6830,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6912,32 +6912,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>247304</t>
+          <t>271903</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>116265</t>
+          <t>241699</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>320883</t>
+          <t>305411</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>25,92%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>29,12%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6947,32 +6947,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>386266</t>
+          <t>426984</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>360619</t>
+          <t>398674</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>412054</t>
+          <t>453628</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>40,29%</t>
+          <t>39,85%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>37,62%</t>
+          <t>37,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>42,98%</t>
+          <t>42,34%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>633571</t>
+          <t>698887</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>432068</t>
+          <t>658918</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>724598</t>
+          <t>740691</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>32,96%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>31,08%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,68%</t>
+          <t>34,93%</t>
         </is>
       </c>
     </row>
@@ -7025,32 +7025,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>945560</t>
+          <t>777014</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>871981</t>
+          <t>743506</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1076599</t>
+          <t>807218</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>79,27%</t>
+          <t>74,08%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>73,1%</t>
+          <t>70,88%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,25%</t>
+          <t>76,96%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7060,32 +7060,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>572385</t>
+          <t>644490</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>546597</t>
+          <t>617846</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>598032</t>
+          <t>672800</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>59,71%</t>
+          <t>60,15%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>57,02%</t>
+          <t>57,66%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>62,38%</t>
+          <t>62,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1517945</t>
+          <t>1421504</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1426918</t>
+          <t>1379700</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1719448</t>
+          <t>1461473</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>70,55%</t>
+          <t>67,04%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>66,32%</t>
+          <t>65,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>79,92%</t>
+          <t>68,92%</t>
         </is>
       </c>
     </row>
@@ -7138,17 +7138,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7173,17 +7173,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>213022</t>
+          <t>242894</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>186567</t>
+          <t>218222</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>236654</t>
+          <t>274696</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>30,23%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>27,17%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>33,58%</t>
+          <t>34,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>472150</t>
+          <t>306405</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>329112</t>
+          <t>282238</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>705811</t>
+          <t>329853</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>50,59%</t>
+          <t>37,72%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>35,26%</t>
+          <t>34,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>75,62%</t>
+          <t>40,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>685172</t>
+          <t>549298</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>532692</t>
+          <t>512626</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>988850</t>
+          <t>590554</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>41,83%</t>
+          <t>34,01%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>31,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>60,37%</t>
+          <t>36,56%</t>
         </is>
       </c>
     </row>
@@ -7368,32 +7368,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>491658</t>
+          <t>560179</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>468026</t>
+          <t>528377</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>518113</t>
+          <t>584851</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>69,77%</t>
+          <t>69,75%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>66,42%</t>
+          <t>65,79%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>73,52%</t>
+          <t>72,83%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7403,32 +7403,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>461216</t>
+          <t>505854</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>227555</t>
+          <t>482406</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>604254</t>
+          <t>530021</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>49,41%</t>
+          <t>62,28%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>59,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>64,74%</t>
+          <t>65,25%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>952874</t>
+          <t>1066034</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>649196</t>
+          <t>1024778</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1105354</t>
+          <t>1102706</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>58,17%</t>
+          <t>65,99%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>39,63%</t>
+          <t>63,44%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>67,48%</t>
+          <t>68,26%</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>296006</t>
+          <t>309898</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>268077</t>
+          <t>280639</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>325198</t>
+          <t>339944</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>31,94%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>28,35%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,09%</t>
+          <t>34,34%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7633,32 +7633,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>437336</t>
+          <t>467450</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>355721</t>
+          <t>439670</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>482392</t>
+          <t>498310</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>39,94%</t>
+          <t>41,77%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>39,29%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>44,06%</t>
+          <t>44,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>733342</t>
+          <t>777348</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>651981</t>
+          <t>737152</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>780673</t>
+          <t>819626</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>36,27%</t>
+          <t>36,86%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>32,25%</t>
+          <t>34,95%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>38,61%</t>
+          <t>38,86%</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>630825</t>
+          <t>680164</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>601633</t>
+          <t>650118</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>658754</t>
+          <t>709423</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>68,06%</t>
+          <t>68,7%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>64,91%</t>
+          <t>65,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>71,08%</t>
+          <t>71,65%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>657596</t>
+          <t>651591</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>612540</t>
+          <t>620731</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>739211</t>
+          <t>679371</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>60,06%</t>
+          <t>58,23%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>55,94%</t>
+          <t>55,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>67,51%</t>
+          <t>60,71%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1288421</t>
+          <t>1331756</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1241090</t>
+          <t>1289478</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1369782</t>
+          <t>1371952</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>63,73%</t>
+          <t>63,14%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>61,39%</t>
+          <t>61,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>67,75%</t>
+          <t>65,05%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7941,32 +7941,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>961331</t>
+          <t>1046564</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>738827</t>
+          <t>991785</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1054383</t>
+          <t>1110818</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>29,62%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>28,07%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>31,44%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7976,32 +7976,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1586668</t>
+          <t>1511326</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1433857</t>
+          <t>1459245</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1977414</t>
+          <t>1566536</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>42,74%</t>
+          <t>40,44%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>38,62%</t>
+          <t>39,05%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>53,27%</t>
+          <t>41,92%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>2547999</t>
+          <t>2557890</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2316995</t>
+          <t>2475849</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2933743</t>
+          <t>2636790</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
+          <t>35,19%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>32,31%</t>
+          <t>34,06%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>40,9%</t>
+          <t>36,27%</t>
         </is>
       </c>
     </row>
@@ -8054,32 +8054,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2498486</t>
+          <t>2486198</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2405434</t>
+          <t>2421944</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2720990</t>
+          <t>2540977</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>72,21%</t>
+          <t>70,38%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>69,52%</t>
+          <t>68,56%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>78,65%</t>
+          <t>71,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8089,32 +8089,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2125612</t>
+          <t>2225628</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1734866</t>
+          <t>2170418</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2278423</t>
+          <t>2277709</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>57,26%</t>
+          <t>59,56%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>46,73%</t>
+          <t>58,08%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>61,38%</t>
+          <t>60,95%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>4624098</t>
+          <t>4711826</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4238354</t>
+          <t>4632926</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4855102</t>
+          <t>4793867</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>64,47%</t>
+          <t>64,81%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>59,1%</t>
+          <t>63,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>67,69%</t>
+          <t>65,94%</t>
         </is>
       </c>
     </row>
@@ -8167,17 +8167,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
